--- a/Sender Gmail Emails/Constancias Frank Part. 2/Datos/Lista.xlsx
+++ b/Sender Gmail Emails/Constancias Frank Part. 2/Datos/Lista.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="11_3F788AF652600E6FE11608154B5DCE3AC74A0458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D8A5308-BED0-46E3-B4FE-79E24DBF2BE4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -491,6 +491,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -779,14 +783,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O91"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="15" max="15" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +837,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -877,7 +881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -921,7 +925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -965,7 +969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1012,7 +1016,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1056,7 +1060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1100,7 +1104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1144,7 +1148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1188,7 +1192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1235,7 +1239,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1326,7 +1330,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1370,7 +1374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1414,7 +1418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1458,7 +1462,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1502,7 +1506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1546,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1593,7 +1597,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1637,7 +1641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1684,7 +1688,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1728,7 +1732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1772,7 +1776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1816,7 +1820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1860,7 +1864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -1904,7 +1908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1948,7 +1952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -1992,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2036,7 +2040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2080,7 +2084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -2124,7 +2128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -2168,7 +2172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -2212,7 +2216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -2256,7 +2260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2300,7 +2304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2347,7 +2351,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2391,7 +2395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -2435,7 +2439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -2479,7 +2483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -2523,7 +2527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -2567,7 +2571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -2611,7 +2615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -2658,7 +2662,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>57</v>
       </c>
@@ -2702,7 +2706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -2746,7 +2750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -2790,7 +2794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -2834,7 +2838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -2881,7 +2885,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -2928,7 +2932,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -2972,7 +2976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3019,7 +3023,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -3063,7 +3067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -3110,7 +3114,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -3154,7 +3158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -3198,7 +3202,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -3242,7 +3246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -3286,7 +3290,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -3333,7 +3337,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -3380,7 +3384,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -3427,7 +3431,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -3471,7 +3475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -3515,7 +3519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -3559,7 +3563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -3603,7 +3607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -3647,7 +3651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -3691,7 +3695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -3735,7 +3739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -3779,7 +3783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -3823,7 +3827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -3867,7 +3871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -3911,7 +3915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -3958,7 +3962,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -4002,7 +4006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -4046,7 +4050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -4093,7 +4097,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -4137,7 +4141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -4181,7 +4185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -4225,7 +4229,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -4269,7 +4273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -4313,7 +4317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -4360,7 +4364,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -4404,7 +4408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -4451,7 +4455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -4498,7 +4502,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -4542,7 +4546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -4589,7 +4593,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>121</v>
       </c>
@@ -4600,7 +4604,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>123</v>
       </c>
@@ -4611,7 +4615,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>125</v>
       </c>
@@ -4622,7 +4626,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>127</v>
       </c>
@@ -4633,7 +4637,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>129</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
     </row>
   </sheetData>
